--- a/weekly_temp/patents_量子算力网.xlsx
+++ b/weekly_temp/patents_量子算力网.xlsx
@@ -413,9 +413,346 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>applicant</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>inventor</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>abstract</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>url</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>用于量子位读出器的补偿脉冲</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>谷歌有限责任公司</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>KELLY, JULIAN SHAW | SANK, DANIEL THOMAS</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>授权专利</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>用于执行量子比特读出的装置和方法。在一个方面,该装置包括:一个以量子比特频率运行的量子比特;一个频率控制器,该频率控制器被配置为控制量子比特频率,并且在量子比特测量操作期间被配置为:确定一个补偿脉冲,该补偿脉冲施加到量子比特时,可以抵消量子比特测量操作期间的量子比特频率变化;以及在量子比特测量操作期间将所确定的补偿脉冲施加到量子比特,以维持量子比特频率。</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=f523a155-4124-4cb1-869d-65ee92a90464&amp;shareId=E1E34EE7-6FBC-6554-BE23-3246B7EF1023&amp;from=EXPORT&amp;signature=Qf10HAnxMoxjgeigLmmNQknQXHN%2FOyApPqsPEsFwyr8%3D&amp;expire=94608000&amp;date=20260605T004024Z&amp;version=1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>用于读取和解码量子信息的设备</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>原子能和替代能源委员会</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>SCHMIDT, QUENTIN | BADETS, FRANCK | THONNART, YVAIN | JADOT, BAPTISTE</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>授权专利</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>本发明涉及一种量子器件,其包括多个量子比特(11、12、…、1M、21…)、一个解复用电路、一条用于将来自所述量子比特的读取信号传输至所述解复用电路的公共传输线,以及针对每个量子比特的量子静电计(S11、S12、…、S1M、S21…),用于在所述公共传输线上传输一个信号,该信号是所述量子比特当前状态和施加于所述量子静电计的周期性激励的函数。该量子器件的独特之处在于,传输至器件中一组量子比特的周期性激励以相同的频率传输。该器件包括用于引入不同相移(Φ1、Φ2、…、ΦM)的移相装置,以及可选的用于在施加于各个量子静电计的激励中引入幅度差异的幅度衰减装置。</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=dde063dd-d9a6-4ba7-ba5b-e50fd97c313c&amp;shareId=E1E34EE7-6FBC-6554-BE23-3246B7EF1023&amp;from=EXPORT&amp;signature=FmV3cEjTPWu%2BS3YzV%2F6OtaXvVUwRIAfWSPJiE2n1nwQ%3D&amp;expire=94608000&amp;date=20260605T004024Z&amp;version=1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>一种在超导量子系统中实现混合维度量子相位门的方法</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>南京大学</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>张钰 | 于扬</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>公开专利</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>本发明属于超导量子计算技术领域，涉及一种在超导量子系统中实现混合维度量子相位门的方法，系统包括：微波腔作为用于承载光子并编码目标量子比特的量子谐振器；超导磁通三能级量子比特作为用作控制位的三能级量子系统，通过电容与微波腔耦合；经典微波脉冲源用于将产生的可控微波驱动场施加于超导磁通三能级量子比特；实现方法是利用超导量子系统中的超导磁通三能级量子比特与微波腔之间的色散耦合作用，并结合施加于超导磁通三能级量子比特的可控微波驱动场，通过一步演化过程，确定性地实现超导磁通三能级量子比特量子态对腔场相位的条件控制；本发明成功率100%，操作可靠性远优于概率性的光学方案。</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=7858d0b7-432f-4508-88e8-e2c3c79fa3f8&amp;shareId=E1E34EE7-6FBC-6554-BE23-3246B7EF1023&amp;from=EXPORT&amp;signature=d0zbxvENPo7C5oj%2FExdIlONDaC7ftusA8TqhfIF5LDQ%3D&amp;expire=94608000&amp;date=20260605T004024Z&amp;version=1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>用于调谐量子计算机的至少两个量子比特之间的相互作用强度的方法和量子计算机</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>伊莱克特伦有限公司</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>帕特里克·胡贝尔 | 克里斯托夫·文德利希</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>公开专利</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>本文中具体说明了用于调谐量子计算机（10）的至少两个量子比特（qb1，qb2）之间的相互作用强度（J）的方法，该方法包括以下步骤：‑ 将第一周期性脉冲序列（1）施加至第一量子比特（qb1），‑ 将第二周期性脉冲序列（2）施加至第二量子比特（qb2），其中，‑ 第一周期性脉冲序列（1）的周期（T）等于第二周期性脉冲序列（2）的周期（T），‑ 使第二周期性脉冲序列（2）的脉冲（21）相对于第一周期性脉冲序列（1）的脉冲（11）时间延迟，以及‑ 通过控制所述时间延迟（Δt）来调谐相互作用强度（J）。此外，本文中具体说明了量子计算机（10）。</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=07a01fc7-1d61-4183-8bd9-b8979bafff6a&amp;shareId=E1E34EE7-6FBC-6554-BE23-3246B7EF1023&amp;from=EXPORT&amp;signature=i9Y4JWZuYTtlsPTUZs84Pd3SQr4qxO3lvUqa%2FIwd2A0%3D&amp;expire=94608000&amp;date=20260605T004024Z&amp;version=1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>用于超导量子比特的非绝热单磁通量子(SFQ)读出的量子计算系统</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>芯科量子公司</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>アレッサンドロ ミアノ | オレグ ムカノフ</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>公开专利</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>本发明提供一种计算或信息处理系统,该系统包括量子计算模块,该量子计算模块利用量子力学器件或电路的量子态执行信息处理或计算。 
+ 【解决方案】该计算或信息处理系统采用基于超导的量子计算模块(例如,超导约瑟夫森结),并构建量子计算模块或器件以及经典数字计算模块或器件,用于各种基于量子计算的应用。此类量子系统包含基于超导约瑟夫森结的量子比特集合,并基于量子比特量子态的叠加和关联/纠缠执行复杂的计算。量子比特器件由量子比特控制电路控制,量子比特读出电路在量子比特控制电路的控制下测量量子比特器件的量子态,并根据测量结果提供量子比特读出。</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=88ad0e44-80d4-439c-b505-c7a5d8291a92&amp;shareId=E1E34EE7-6FBC-6554-BE23-3246B7EF1023&amp;from=EXPORT&amp;signature=G9LfKTB8JnqoRI2Dn8R4dRfNs%2F2jOb1qytdxeOVTk6c%3D&amp;expire=94608000&amp;date=20260605T004024Z&amp;version=1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>超导量子处理电路中的可调谐量子比特器件</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>RIGETTI &amp; CO INC</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>SETE, EYOB A. | CHEN, ANGELA Q. | POLETTO, STEFANO | KULSHRESHTHA, SHOBHAN | MANENTI, RICCARDO</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>授权专利</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>一般而言,超导量子处理电路包含一个可调谐量子比特器件。该可调谐量子比特器件包含一个电路环路,该电路环路配置成在可调谐量子比特器件工作期间接收磁通量,该磁通量控制该可调谐量子比特器件的量子比特频率。在一些实施例中,该电路环路由以下部分组成:一个非线性电路元件和一个或多个线性电路元件。该单个非线性电路元件是连接在第一电路节点和第二电路节点之间的约瑟夫森结。该一个或多个线性电路元件包括一个与连接在第一电路节点和第二电路节点之间的约瑟夫森结并联的线性电感器。</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=7ee4ebb7-bf1f-4709-9bd8-e2c11c904371&amp;shareId=E1E34EE7-6FBC-6554-BE23-3246B7EF1023&amp;from=EXPORT&amp;signature=113QyBsuqSB7ew5nF5t9X7v8ckZq86qN%2FYBOiHEoKcY%3D&amp;expire=94608000&amp;date=20260605T004024Z&amp;version=1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>带有嵌入式读出的紧凑型硅量子比特单元</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>量子运动科技有限公司</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>GONZALEZ-ZALBA, MIGUEL FERNANDO</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>授权专利</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>本发明公开了一种量子器件,该器件具有用于执行量子比特测量或读出的LC谐振器电路。该器件包括硅层( 601 ),介电层( 603 ) 布置在硅层上并与硅层形成功能界面( 601 ),第一金属区( 614 )布置在介电层上603以及第二个金属区域( 624 )布置在介电层上603并与第一金属区域横向分离( 614第一和第二金属区( 614, 624 )被布置成电连接,使得可以在第一和第二金属区域下方感应出一个双量子点,形成一个具有第一态和第二态的量子比特( 614, 624在功能界面处。双量子点提供了一个电容 C 1在LC谐振器电路中,双量子点的电容取决于量子比特的状态。第一个金属区域( 614 ) 提供一个电感器 L 1在 LC 谐振器电路中,LC 谐振器电路的谐振频率取决于量子比特的状态,因此可以测量或推断量子比特的状态。</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=c4572404-b8ad-47b4-9a02-11d0d900b01a&amp;shareId=E1E34EE7-6FBC-6554-BE23-3246B7EF1023&amp;from=EXPORT&amp;signature=hfKywHVMw%2BVdoUO9gdOfjExUoagn07uL2GPrjy0yOIY%3D&amp;expire=94608000&amp;date=20260605T004024Z&amp;version=1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>用于量子计算误差抑制的分层噪声自适应控制系统及方法</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>IEN ARCHITECT OFFICE CO LTD</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>정찬희</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>公开专利</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>本发明涉及一种用于减少量子计算环境中物理误差的分层控制系统和方法。本发明利用包含室温控制代理(RTAA)和近端硬件控制器(NHC)的双层控制结构,实现了实时脉冲控制和自适应噪声参数更新的并行执行。 
+具体而言,本发明包括:(1) 噪声不对称反向镜像 (NAEM),用于反转超导量子比特 T1 弛豫方向的不对称性;(2) 节律频谱指纹识别 (RSF),通过对门脉冲施加周期性调制,为解码器输入提供结构特征量;(3) 经典顺序引导序列化 (CGS),用作辅助元数据通道,用于检测经典控制通道的顺序计数器异常;以及 (4) 分层自适应控制 (HAC),用于分离室温控制代理和近端硬件控制器的角色。 
+本发明涉及一种在保持现有电路功能结构的同时自适应地优化执行控制参数的技术,而对电路结构本身的改变,例如逻辑量子比特和物理量子比特之间的重新映射、重新排列门执行顺序或重新配置电路深度,并非本发明的直接主题。</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=4e488ee2-feac-4374-af22-02ceaaf24a98&amp;shareId=E1E34EE7-6FBC-6554-BE23-3246B7EF1023&amp;from=EXPORT&amp;signature=n1OpBWABvcgiGtIaeCREOf1jZGqGWQc8e7CdYxtG6Mg%3D&amp;expire=94608000&amp;date=20260605T004024Z&amp;version=1.0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/weekly_temp/patents_量子算力网.xlsx
+++ b/weekly_temp/patents_量子算力网.xlsx
@@ -413,346 +413,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>applicant</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>inventor</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>abstract</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>url</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>用于量子位读出器的补偿脉冲</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>谷歌有限责任公司</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>KELLY, JULIAN SHAW | SANK, DANIEL THOMAS</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>授权专利</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>用于执行量子比特读出的装置和方法。在一个方面,该装置包括:一个以量子比特频率运行的量子比特;一个频率控制器,该频率控制器被配置为控制量子比特频率,并且在量子比特测量操作期间被配置为:确定一个补偿脉冲,该补偿脉冲施加到量子比特时,可以抵消量子比特测量操作期间的量子比特频率变化;以及在量子比特测量操作期间将所确定的补偿脉冲施加到量子比特,以维持量子比特频率。</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=f523a155-4124-4cb1-869d-65ee92a90464&amp;shareId=E1E34EE7-6FBC-6554-BE23-3246B7EF1023&amp;from=EXPORT&amp;signature=Qf10HAnxMoxjgeigLmmNQknQXHN%2FOyApPqsPEsFwyr8%3D&amp;expire=94608000&amp;date=20260605T004024Z&amp;version=1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>用于读取和解码量子信息的设备</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>原子能和替代能源委员会</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>SCHMIDT, QUENTIN | BADETS, FRANCK | THONNART, YVAIN | JADOT, BAPTISTE</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>授权专利</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>本发明涉及一种量子器件,其包括多个量子比特(11、12、…、1M、21…)、一个解复用电路、一条用于将来自所述量子比特的读取信号传输至所述解复用电路的公共传输线,以及针对每个量子比特的量子静电计(S11、S12、…、S1M、S21…),用于在所述公共传输线上传输一个信号,该信号是所述量子比特当前状态和施加于所述量子静电计的周期性激励的函数。该量子器件的独特之处在于,传输至器件中一组量子比特的周期性激励以相同的频率传输。该器件包括用于引入不同相移(Φ1、Φ2、…、ΦM)的移相装置,以及可选的用于在施加于各个量子静电计的激励中引入幅度差异的幅度衰减装置。</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=dde063dd-d9a6-4ba7-ba5b-e50fd97c313c&amp;shareId=E1E34EE7-6FBC-6554-BE23-3246B7EF1023&amp;from=EXPORT&amp;signature=FmV3cEjTPWu%2BS3YzV%2F6OtaXvVUwRIAfWSPJiE2n1nwQ%3D&amp;expire=94608000&amp;date=20260605T004024Z&amp;version=1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>一种在超导量子系统中实现混合维度量子相位门的方法</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>南京大学</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>张钰 | 于扬</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>公开专利</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>本发明属于超导量子计算技术领域，涉及一种在超导量子系统中实现混合维度量子相位门的方法，系统包括：微波腔作为用于承载光子并编码目标量子比特的量子谐振器；超导磁通三能级量子比特作为用作控制位的三能级量子系统，通过电容与微波腔耦合；经典微波脉冲源用于将产生的可控微波驱动场施加于超导磁通三能级量子比特；实现方法是利用超导量子系统中的超导磁通三能级量子比特与微波腔之间的色散耦合作用，并结合施加于超导磁通三能级量子比特的可控微波驱动场，通过一步演化过程，确定性地实现超导磁通三能级量子比特量子态对腔场相位的条件控制；本发明成功率100%，操作可靠性远优于概率性的光学方案。</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=7858d0b7-432f-4508-88e8-e2c3c79fa3f8&amp;shareId=E1E34EE7-6FBC-6554-BE23-3246B7EF1023&amp;from=EXPORT&amp;signature=d0zbxvENPo7C5oj%2FExdIlONDaC7ftusA8TqhfIF5LDQ%3D&amp;expire=94608000&amp;date=20260605T004024Z&amp;version=1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>用于调谐量子计算机的至少两个量子比特之间的相互作用强度的方法和量子计算机</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>伊莱克特伦有限公司</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>帕特里克·胡贝尔 | 克里斯托夫·文德利希</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>公开专利</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>本文中具体说明了用于调谐量子计算机（10）的至少两个量子比特（qb1，qb2）之间的相互作用强度（J）的方法，该方法包括以下步骤：‑ 将第一周期性脉冲序列（1）施加至第一量子比特（qb1），‑ 将第二周期性脉冲序列（2）施加至第二量子比特（qb2），其中，‑ 第一周期性脉冲序列（1）的周期（T）等于第二周期性脉冲序列（2）的周期（T），‑ 使第二周期性脉冲序列（2）的脉冲（21）相对于第一周期性脉冲序列（1）的脉冲（11）时间延迟，以及‑ 通过控制所述时间延迟（Δt）来调谐相互作用强度（J）。此外，本文中具体说明了量子计算机（10）。</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=07a01fc7-1d61-4183-8bd9-b8979bafff6a&amp;shareId=E1E34EE7-6FBC-6554-BE23-3246B7EF1023&amp;from=EXPORT&amp;signature=i9Y4JWZuYTtlsPTUZs84Pd3SQr4qxO3lvUqa%2FIwd2A0%3D&amp;expire=94608000&amp;date=20260605T004024Z&amp;version=1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>用于超导量子比特的非绝热单磁通量子(SFQ)读出的量子计算系统</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>芯科量子公司</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>アレッサンドロ ミアノ | オレグ ムカノフ</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>公开专利</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>本发明提供一种计算或信息处理系统,该系统包括量子计算模块,该量子计算模块利用量子力学器件或电路的量子态执行信息处理或计算。 
- 【解决方案】该计算或信息处理系统采用基于超导的量子计算模块(例如,超导约瑟夫森结),并构建量子计算模块或器件以及经典数字计算模块或器件,用于各种基于量子计算的应用。此类量子系统包含基于超导约瑟夫森结的量子比特集合,并基于量子比特量子态的叠加和关联/纠缠执行复杂的计算。量子比特器件由量子比特控制电路控制,量子比特读出电路在量子比特控制电路的控制下测量量子比特器件的量子态,并根据测量结果提供量子比特读出。</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=88ad0e44-80d4-439c-b505-c7a5d8291a92&amp;shareId=E1E34EE7-6FBC-6554-BE23-3246B7EF1023&amp;from=EXPORT&amp;signature=G9LfKTB8JnqoRI2Dn8R4dRfNs%2F2jOb1qytdxeOVTk6c%3D&amp;expire=94608000&amp;date=20260605T004024Z&amp;version=1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>超导量子处理电路中的可调谐量子比特器件</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>RIGETTI &amp; CO INC</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>SETE, EYOB A. | CHEN, ANGELA Q. | POLETTO, STEFANO | KULSHRESHTHA, SHOBHAN | MANENTI, RICCARDO</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>授权专利</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>一般而言,超导量子处理电路包含一个可调谐量子比特器件。该可调谐量子比特器件包含一个电路环路,该电路环路配置成在可调谐量子比特器件工作期间接收磁通量,该磁通量控制该可调谐量子比特器件的量子比特频率。在一些实施例中,该电路环路由以下部分组成:一个非线性电路元件和一个或多个线性电路元件。该单个非线性电路元件是连接在第一电路节点和第二电路节点之间的约瑟夫森结。该一个或多个线性电路元件包括一个与连接在第一电路节点和第二电路节点之间的约瑟夫森结并联的线性电感器。</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=7ee4ebb7-bf1f-4709-9bd8-e2c11c904371&amp;shareId=E1E34EE7-6FBC-6554-BE23-3246B7EF1023&amp;from=EXPORT&amp;signature=113QyBsuqSB7ew5nF5t9X7v8ckZq86qN%2FYBOiHEoKcY%3D&amp;expire=94608000&amp;date=20260605T004024Z&amp;version=1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>带有嵌入式读出的紧凑型硅量子比特单元</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>量子运动科技有限公司</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>GONZALEZ-ZALBA, MIGUEL FERNANDO</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>授权专利</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>本发明公开了一种量子器件,该器件具有用于执行量子比特测量或读出的LC谐振器电路。该器件包括硅层( 601 ),介电层( 603 ) 布置在硅层上并与硅层形成功能界面( 601 ),第一金属区( 614 )布置在介电层上603以及第二个金属区域( 624 )布置在介电层上603并与第一金属区域横向分离( 614第一和第二金属区( 614, 624 )被布置成电连接,使得可以在第一和第二金属区域下方感应出一个双量子点,形成一个具有第一态和第二态的量子比特( 614, 624在功能界面处。双量子点提供了一个电容 C 1在LC谐振器电路中,双量子点的电容取决于量子比特的状态。第一个金属区域( 614 ) 提供一个电感器 L 1在 LC 谐振器电路中,LC 谐振器电路的谐振频率取决于量子比特的状态,因此可以测量或推断量子比特的状态。</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=c4572404-b8ad-47b4-9a02-11d0d900b01a&amp;shareId=E1E34EE7-6FBC-6554-BE23-3246B7EF1023&amp;from=EXPORT&amp;signature=hfKywHVMw%2BVdoUO9gdOfjExUoagn07uL2GPrjy0yOIY%3D&amp;expire=94608000&amp;date=20260605T004024Z&amp;version=1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>用于量子计算误差抑制的分层噪声自适应控制系统及方法</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>IEN ARCHITECT OFFICE CO LTD</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>정찬희</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>公开专利</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>本发明涉及一种用于减少量子计算环境中物理误差的分层控制系统和方法。本发明利用包含室温控制代理(RTAA)和近端硬件控制器(NHC)的双层控制结构,实现了实时脉冲控制和自适应噪声参数更新的并行执行。 
-具体而言,本发明包括:(1) 噪声不对称反向镜像 (NAEM),用于反转超导量子比特 T1 弛豫方向的不对称性;(2) 节律频谱指纹识别 (RSF),通过对门脉冲施加周期性调制,为解码器输入提供结构特征量;(3) 经典顺序引导序列化 (CGS),用作辅助元数据通道,用于检测经典控制通道的顺序计数器异常;以及 (4) 分层自适应控制 (HAC),用于分离室温控制代理和近端硬件控制器的角色。 
-本发明涉及一种在保持现有电路功能结构的同时自适应地优化执行控制参数的技术,而对电路结构本身的改变,例如逻辑量子比特和物理量子比特之间的重新映射、重新排列门执行顺序或重新配置电路深度,并非本发明的直接主题。</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=4e488ee2-feac-4374-af22-02ceaaf24a98&amp;shareId=E1E34EE7-6FBC-6554-BE23-3246B7EF1023&amp;from=EXPORT&amp;signature=n1OpBWABvcgiGtIaeCREOf1jZGqGWQc8e7CdYxtG6Mg%3D&amp;expire=94608000&amp;date=20260605T004024Z&amp;version=1.0</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/weekly_temp/patents_量子算力网.xlsx
+++ b/weekly_temp/patents_量子算力网.xlsx
@@ -413,9 +413,121 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>applicant</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>inventor</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>abstract</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>url</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>任务处理方法、装置、介质、设备及量超智融合计算系统</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>之江实验室</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>刘振德 | 刘鹏 | 吴文勋</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>公开专利</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>本申请提供一种任务处理方法、装置、介质、设备及量超智融合计算系统，其中，本申请通过构建高性能的量子计算芯片互连，形成大规模的量子计算集群，以增加可用的量子比特数，提高量子计算的并行性和能效。同时，提出一种基于共享资源模型的新型计算范式，为众核控制芯片、智能计算模块和QPUs组成的量超智融合计算系统设计交互模式，以消除通信延迟并最大限度地提高系统在执行算法任务时的计算速度。</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=c064a5fb-80de-461c-a536-63b814cfc9bb&amp;shareId=04B657FB-5FD3-980C-1E12-7E80C58E4C69&amp;from=EXPORT&amp;signature=PifAmVWwVWsJOxHrRxc538B2kS1kjMAvjZh7tJqJ990%3D&amp;expire=94608000&amp;date=20260710T003001Z&amp;version=1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>加速器/量子计算功能即服务的检查点系统</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>戴尔产品有限公司</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>SANTAUS, BENJAMIN | FONG, VICTOR | HEALY, BRENDAN BURNS | PINHO, RÔMULO TEIXEIRA DE ABREU</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>授权专利</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>本发明公开了一种加速器功能即服务系统。该系统可接收包含计算机(CPU)部分和加速器部分的作业。当执行加速器部分时,系统会确定与加速器返回结果时间相关的执行时间。分配给该作业或 CPU 部分的资源或其一部分至少在执行期间会被释放或重新分配给其他作业。当从加速器收到结果时,该作业会被排队等待接收资源。</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=47319600-0a46-4157-911f-64aa2138915f&amp;shareId=04B657FB-5FD3-980C-1E12-7E80C58E4C69&amp;from=EXPORT&amp;signature=pPPfOD6IFmYg%2FKxd%2BqPUS%2BRZSSJHLS5LjemIHN1pDdI%3D&amp;expire=94608000&amp;date=20260710T003001Z&amp;version=1.0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/weekly_temp/patents_量子算力网.xlsx
+++ b/weekly_temp/patents_量子算力网.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,17 +456,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>任务处理方法、装置、介质、设备及量超智融合计算系统</t>
+          <t>基于数字量子计算的算力网络DDoS检测方法及系统</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>之江实验室</t>
+          <t>深圳市永达电子信息股份有限公司</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>刘振德 | 刘鹏 | 吴文勋</t>
+          <t>戚建淮 | 胡金华 | 郑伟范 | 王胤丞 | 李雨鑫 | 成飏</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -476,54 +476,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>本申请提供一种任务处理方法、装置、介质、设备及量超智融合计算系统，其中，本申请通过构建高性能的量子计算芯片互连，形成大规模的量子计算集群，以增加可用的量子比特数，提高量子计算的并行性和能效。同时，提出一种基于共享资源模型的新型计算范式，为众核控制芯片、智能计算模块和QPUs组成的量超智融合计算系统设计交互模式，以消除通信延迟并最大限度地提高系统在执行算法任务时的计算速度。</t>
+          <t>本发明公开了基于数字量子计算的算力网络DDoS检测方法及系统，涉及网络空间安全管控技术领域。本发明包括：通过分散检测点采集管辖区域内的实时网络流量数据，构建基于量子随机行走采样的图神经网络DDoS检测算法，执行量子随机行走得到各节点的量子概率分布；对每个目标节点的邻居节点进行量子概率加权的无放回采样，得到采样邻居集合；通过图采样聚合网络对采样邻居集合进行消息传递；通过联邦学习架构将本地模型参数上传至安全管理中心，输出DDoS攻击检测结果。本发明实现了基于图结构的DDoS流量特征提取，并利用量子随机行走引导的邻居采样机制，完成对DDoS攻击的实时识别与检测。</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=c064a5fb-80de-461c-a536-63b814cfc9bb&amp;shareId=04B657FB-5FD3-980C-1E12-7E80C58E4C69&amp;from=EXPORT&amp;signature=PifAmVWwVWsJOxHrRxc538B2kS1kjMAvjZh7tJqJ990%3D&amp;expire=94608000&amp;date=20260710T003001Z&amp;version=1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>加速器/量子计算功能即服务的检查点系统</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>戴尔产品有限公司</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>SANTAUS, BENJAMIN | FONG, VICTOR | HEALY, BRENDAN BURNS | PINHO, RÔMULO TEIXEIRA DE ABREU</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>授权专利</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>本发明公开了一种加速器功能即服务系统。该系统可接收包含计算机(CPU)部分和加速器部分的作业。当执行加速器部分时,系统会确定与加速器返回结果时间相关的执行时间。分配给该作业或 CPU 部分的资源或其一部分至少在执行期间会被释放或重新分配给其他作业。当从加速器收到结果时,该作业会被排队等待接收资源。</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=47319600-0a46-4157-911f-64aa2138915f&amp;shareId=04B657FB-5FD3-980C-1E12-7E80C58E4C69&amp;from=EXPORT&amp;signature=pPPfOD6IFmYg%2FKxd%2BqPUS%2BRZSSJHLS5LjemIHN1pDdI%3D&amp;expire=94608000&amp;date=20260710T003001Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=20344211-20e9-4642-9bbd-b4bb936c09c7&amp;shareId=3162272E-8550-8EBD-1G9B-7218D7ED1ECB&amp;from=EXPORT&amp;signature=6J0aJQXK%2BBTe6yhANVvKqT2sEBKtS6rI1g0cLlS2RbQ%3D&amp;expire=94608000&amp;date=20260717T011238Z&amp;version=1.0</t>
         </is>
       </c>
     </row>

--- a/weekly_temp/patents_量子算力网.xlsx
+++ b/weekly_temp/patents_量子算力网.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,17 +456,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>基于数字量子计算的算力网络DDoS检测方法及系统</t>
+          <t>一种基于大语言模型的量子算法工作流处理方法和系统</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>深圳市永达电子信息股份有限公司</t>
+          <t>北京量坤科技有限公司</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>戚建淮 | 胡金华 | 郑伟范 | 王胤丞 | 李雨鑫 | 成飏</t>
+          <t>罗军 | 郭雨尘 | 吕定顺 | 柴琛林 | 李子航</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -476,17 +476,91 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>本发明公开了基于数字量子计算的算力网络DDoS检测方法及系统，涉及网络空间安全管控技术领域。本发明包括：通过分散检测点采集管辖区域内的实时网络流量数据，构建基于量子随机行走采样的图神经网络DDoS检测算法，执行量子随机行走得到各节点的量子概率分布；对每个目标节点的邻居节点进行量子概率加权的无放回采样，得到采样邻居集合；通过图采样聚合网络对采样邻居集合进行消息传递；通过联邦学习架构将本地模型参数上传至安全管理中心，输出DDoS攻击检测结果。本发明实现了基于图结构的DDoS流量特征提取，并利用量子随机行走引导的邻居采样机制，完成对DDoS攻击的实时识别与检测。</t>
+          <t>本发明公开了一种基于大语言模型的量子算法工作流处理方法和系统，属于量子算法技术领域。方法包括会话服务子系统动态同步原子化算法清单，原子化算法清单由算力服务子系统维护；会话服务子系统进行意图识别，构造上下文；LLM根据输入语言、上下文和回流的告警信息，生成DAG结构提议；预执行校验关口进行预执行校验，并生成校验结果；会话服务子系统将告警信息回流至LLM；算力服务子系统异步执行DAG结构提议。本申请通过对输入语言进行意图识别，当为算法意图时生成DAG结构提议，并通过预执行校验关口进行校验，并在校验通过后再执行DAG提议有效避免了算力浪费；在校验未通过时通过回流信息修正原有DAG提议形成自动修正的闭环。</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=20344211-20e9-4642-9bbd-b4bb936c09c7&amp;shareId=3162272E-8550-8EBD-1G9B-7218D7ED1ECB&amp;from=EXPORT&amp;signature=6J0aJQXK%2BBTe6yhANVvKqT2sEBKtS6rI1g0cLlS2RbQ%3D&amp;expire=94608000&amp;date=20260717T011238Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=55354915-3837-468e-b9a1-4b5c25f14638&amp;shareId=6G63BFE2-F5F7-8FFG-CEG2-BB8B6G88EG91&amp;from=EXPORT&amp;signature=MQA1JCxm1s8m4aop6sM7kpiF2Iwlx4tsJltr183mvJs%3D&amp;expire=94608000&amp;date=20260821T055131Z&amp;version=1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>任务的排程方法、装置、系统、电子设备及存储介质</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>珠海联云科技有限公司 | 珠海格力电器股份有限公司</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>罗琴 | 张俊杰 | 王馨营 | 李子轩 | 陈丹丹</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>公开专利</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>本发明提供了一种任务的排程方法、装置、系统、电子设备及存储介质，涉及排程优化技术领域，所述方法包括：构建与排程任务对应的多尺度图网络，多尺度图网络包括任务节点；提取任务节点的节点特征，并根据节点特征对任务节点进行筛选，获得满足条件的关键瓶颈节点；将关键瓶颈节点对应的可选调度状态映射为量子比特；获取用于量子退化演化的目标能量函数，并根据目标能量函数对量子比特构成的瓶颈系统进行演化，获得关键瓶颈节点的优化状态；根据优化状态进行排程，生成针对排程任务的排程方案，从而实现了复杂排程场景下的高效协同优化，提升了求解质量和计算效率，使得所生成的排程方案能够兼顾不同时间尺度的全局一致性与全局可行性。</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=acdb5b08-6a5f-4859-ac93-eecb870f622f&amp;shareId=6G63BFE2-F5F7-8FFG-CEG2-BB8B6G88EG91&amp;from=EXPORT&amp;signature=f3rhxafCvEp9aBudv6nMG%2BqINSAKk9Q2HcMJreHxNF0%3D&amp;expire=94608000&amp;date=20260821T055131Z&amp;version=1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>一种基于FPGA、CPLD与量子芯片的三层异构安全加速架构</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>长沙方舟人工智能科技发展有限公司</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>腾启</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>公开专利</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>本发明公开了一种基于FPGA、CPLD与量子芯片的三层异构安全加速架构，包括：FPGA算力执行层、CPLD硬件裁决层和量子芯片安全熵源层，三层硬件单元通过硬件引脚互连，实现物理层级隔离、时序同步与功能联动，在上电、运行、异常触发全流程中通过硬件引脚级信号握手校验形成联动闭环，全程通过硬件引脚级信号交互实现安全控制逻辑，不依赖CPU及软件执行安全控制逻辑；通过采用FPGA‑CPLD‑量子芯片三层异构安全架构，依托独立硬件级CPLD实现上电管控、异常熔断与端口防护，脱离软件依赖，规避FPGA自监督漏洞；量子密钥经独立通道传输，阻断密钥泄露风险。算力与安全物理隔离，保障运算效率，结合硬件联动闭环与量子熵源，有效抵御高阶攻击，强化设备底层硬件防护能力。</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=01b55ce1-1c1a-480b-89c8-cade498d5dd5&amp;shareId=6G63BFE2-F5F7-8FFG-CEG2-BB8B6G88EG91&amp;from=EXPORT&amp;signature=BGXSqsn5qdAeR1uTwdzwkFwDDQC7doNNccHcA7Nx2Ic%3D&amp;expire=94608000&amp;date=20260821T055131Z&amp;version=1.0</t>
         </is>
       </c>
     </row>

--- a/weekly_temp/patents_量子算力网.xlsx
+++ b/weekly_temp/patents_量子算力网.xlsx
@@ -413,158 +413,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>applicant</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>inventor</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>abstract</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>url</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>一种基于大语言模型的量子算法工作流处理方法和系统</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>北京量坤科技有限公司</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>罗军 | 郭雨尘 | 吕定顺 | 柴琛林 | 李子航</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>公开专利</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>本发明公开了一种基于大语言模型的量子算法工作流处理方法和系统，属于量子算法技术领域。方法包括会话服务子系统动态同步原子化算法清单，原子化算法清单由算力服务子系统维护；会话服务子系统进行意图识别，构造上下文；LLM根据输入语言、上下文和回流的告警信息，生成DAG结构提议；预执行校验关口进行预执行校验，并生成校验结果；会话服务子系统将告警信息回流至LLM；算力服务子系统异步执行DAG结构提议。本申请通过对输入语言进行意图识别，当为算法意图时生成DAG结构提议，并通过预执行校验关口进行校验，并在校验通过后再执行DAG提议有效避免了算力浪费；在校验未通过时通过回流信息修正原有DAG提议形成自动修正的闭环。</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=55354915-3837-468e-b9a1-4b5c25f14638&amp;shareId=6G63BFE2-F5F7-8FFG-CEG2-BB8B6G88EG91&amp;from=EXPORT&amp;signature=MQA1JCxm1s8m4aop6sM7kpiF2Iwlx4tsJltr183mvJs%3D&amp;expire=94608000&amp;date=20260821T055131Z&amp;version=1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>任务的排程方法、装置、系统、电子设备及存储介质</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>珠海联云科技有限公司 | 珠海格力电器股份有限公司</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>罗琴 | 张俊杰 | 王馨营 | 李子轩 | 陈丹丹</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>公开专利</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>本发明提供了一种任务的排程方法、装置、系统、电子设备及存储介质，涉及排程优化技术领域，所述方法包括：构建与排程任务对应的多尺度图网络，多尺度图网络包括任务节点；提取任务节点的节点特征，并根据节点特征对任务节点进行筛选，获得满足条件的关键瓶颈节点；将关键瓶颈节点对应的可选调度状态映射为量子比特；获取用于量子退化演化的目标能量函数，并根据目标能量函数对量子比特构成的瓶颈系统进行演化，获得关键瓶颈节点的优化状态；根据优化状态进行排程，生成针对排程任务的排程方案，从而实现了复杂排程场景下的高效协同优化，提升了求解质量和计算效率，使得所生成的排程方案能够兼顾不同时间尺度的全局一致性与全局可行性。</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=acdb5b08-6a5f-4859-ac93-eecb870f622f&amp;shareId=6G63BFE2-F5F7-8FFG-CEG2-BB8B6G88EG91&amp;from=EXPORT&amp;signature=f3rhxafCvEp9aBudv6nMG%2BqINSAKk9Q2HcMJreHxNF0%3D&amp;expire=94608000&amp;date=20260821T055131Z&amp;version=1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>一种基于FPGA、CPLD与量子芯片的三层异构安全加速架构</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>长沙方舟人工智能科技发展有限公司</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>腾启</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>公开专利</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>本发明公开了一种基于FPGA、CPLD与量子芯片的三层异构安全加速架构，包括：FPGA算力执行层、CPLD硬件裁决层和量子芯片安全熵源层，三层硬件单元通过硬件引脚互连，实现物理层级隔离、时序同步与功能联动，在上电、运行、异常触发全流程中通过硬件引脚级信号握手校验形成联动闭环，全程通过硬件引脚级信号交互实现安全控制逻辑，不依赖CPU及软件执行安全控制逻辑；通过采用FPGA‑CPLD‑量子芯片三层异构安全架构，依托独立硬件级CPLD实现上电管控、异常熔断与端口防护，脱离软件依赖，规避FPGA自监督漏洞；量子密钥经独立通道传输，阻断密钥泄露风险。算力与安全物理隔离，保障运算效率，结合硬件联动闭环与量子熵源，有效抵御高阶攻击，强化设备底层硬件防护能力。</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=01b55ce1-1c1a-480b-89c8-cade498d5dd5&amp;shareId=6G63BFE2-F5F7-8FFG-CEG2-BB8B6G88EG91&amp;from=EXPORT&amp;signature=BGXSqsn5qdAeR1uTwdzwkFwDDQC7doNNccHcA7Nx2Ic%3D&amp;expire=94608000&amp;date=20260821T055131Z&amp;version=1.0</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>